--- a/public/contests/ejoy2027/standing_detailed_Day1_en.xlsx
+++ b/public/contests/ejoy2027/standing_detailed_Day1_en.xlsx
@@ -89,7 +89,7 @@
     <t>BGR117</t>
   </si>
   <si>
-    <t>Kaloyan Hristov Ketsarov</t>
+    <t>Kaloyan Hristov Keratsov</t>
   </si>
   <si>
     <t>BGR107</t>
